--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Agricultural Production - Major Commercial Crops.xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Agricultural Production - Major Commercial Crops.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>Oilseeds</t>
   </si>
@@ -283,16 +283,15 @@
     <t>(Lakhs Tonnes)</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes : 1. Data for 2025-26    are based on First Advance Estimates.
-            2. Data for 1960-61 to 1969-70 relate to total five major oilseeds viz., groundnut,  castorseed, sesamum, rapeseed and mustard and linseed.
-            3. Data for 1950-51 and 1951-52 relate to Jute crop only.
-            4. Oilseed data comprises total for nine oilseeds out of the eleven in all.
-            5. Coffee and Tea data measured in Lakh kg.
-            6. Cotton data measured in Lakh bales of 170 kg.each.
-            7. Raw jute and the mesta data measured in Lakh bales of 180 kg. each.
-            8. - : Not Available.
+    <t xml:space="preserve">Notes : 1. Data for 2025-26 are based on Third Advance Estimates.
+            2. Data for 1969-70 relate to total five major oilseeds viz., groundnut, castorseed, sesamum, rapeseed and mustard, and linseed.
+            3. Oilseed data comprises total for nine oilseeds out of the eleven in all.
+            4. Coffee and Tea data measured in lacs kg.
+            5. Cotton data measured in lacs bales of 170 kg each.
+            6. Raw jute and the mesta data measured in lacs bales of 180 kg each.
+            7. - : Not Available.
 Also see Notes on Tables.
-Source : Ministry of Agriculture &amp; Farmers Welfare, Government of India, Coffee Board of India, Tea Board of India.</t>
+Source  :  Ministry of Agriculture &amp; Farmers Welfare, Government of India, Coffee Board of India, Tea Board of India.</t>
   </si>
 </sst>
 </file>
@@ -510,11 +509,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:L87"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="2" width="13.138612" customWidth="1"/>
     <col min="3" max="12" width="14.541796" customWidth="1"/>
+    <col min="13" max="13" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
@@ -626,31 +626,31 @@
         <v>12</v>
       </c>
       <c r="C9" s="11">
-        <v>110.93</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>13</v>
+        <v>130.74</v>
+      </c>
+      <c r="D9" s="11">
+        <v>137.68</v>
       </c>
       <c r="E9" s="11">
-        <v>142.66</v>
+        <v>125.96</v>
       </c>
       <c r="F9" s="11">
-        <v>275.63</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>13</v>
+        <v>430.59</v>
+      </c>
+      <c r="G9" s="11">
+        <v>3730</v>
       </c>
       <c r="H9" s="11">
-        <v>292.15</v>
+        <v>290.24</v>
       </c>
       <c r="I9" s="11">
-        <v>83.45</v>
+        <v>94.03</v>
       </c>
       <c r="J9" s="11">
-        <v>4756.14</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>13</v>
+        <v>5000.63</v>
+      </c>
+      <c r="K9" s="11">
+        <v>13827.4</v>
       </c>
       <c r="L9" s="12" t="s">
         <v>13</v>
@@ -3282,7 +3282,7 @@
       </c>
     </row>
     <row r="85" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
-    <row r="86" s="1" customFormat="1" ht="121.5924" customHeight="1">
+    <row r="86" s="1" customFormat="1" ht="116.2594" customHeight="1">
       <c r="B86" s="20" t="s">
         <v>91</v>
       </c>
@@ -3293,12 +3293,15 @@
       <c r="G86" s="20"/>
       <c r="H86" s="20"/>
       <c r="I86" s="20"/>
-    </row>
+      <c r="J86" s="20"/>
+      <c r="K86" s="20"/>
+    </row>
+    <row r="87" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B86:I86"/>
+    <mergeCell ref="B86:K86"/>
     <mergeCell ref="C6:F6"/>
   </mergeCells>
   <pageSetup paperSize="120" scale="100" orientation="landscape"/>
